--- a/Configs/GameConfig/Datas/Role.xlsx
+++ b/Configs/GameConfig/Datas/Role.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380"/>
+    <workbookView windowHeight="17940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>角色1002</t>
-  </si>
-  <si>
-    <t>Batty_B</t>
   </si>
   <si>
     <t>角色1003</t>
@@ -153,10 +150,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -168,12 +165,49 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
@@ -181,31 +215,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,10 +263,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,6 +278,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -274,38 +293,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,25 +317,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,19 +383,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,48 +425,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -434,12 +455,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -452,55 +467,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,6 +508,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -548,16 +563,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,26 +608,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -619,145 +616,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1181,7 +1178,7 @@
         <v>16</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
         <v>16</v>
@@ -1338,8 +1335,8 @@
       <c r="D6" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
-        <v>39</v>
+      <c r="E6">
+        <v>1002</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -1348,10 +1345,10 @@
         <v>1001</v>
       </c>
       <c r="H6">
-        <v>1002</v>
+        <v>10011</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -1360,7 +1357,7 @@
         <v>50</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -1369,7 +1366,7 @@
         <v>1000</v>
       </c>
       <c r="O6">
-        <v>100101</v>
+        <v>100201</v>
       </c>
     </row>
     <row r="7" spans="2:15">
@@ -1377,13 +1374,13 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1421,13 +1418,13 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>13</v>

--- a/Configs/GameConfig/Datas/Role.xlsx
+++ b/Configs/GameConfig/Datas/Role.xlsx
@@ -150,9 +150,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -171,6 +171,89 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -179,6 +262,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -186,123 +294,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,67 +317,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,13 +473,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,97 +497,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,16 +515,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -562,19 +553,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -594,17 +598,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,10 +616,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -628,31 +628,34 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,97 +667,94 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1310,7 +1310,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1354,7 +1354,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>0.8</v>
@@ -1398,7 +1398,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1442,7 +1442,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>5</v>

--- a/Configs/GameConfig/Datas/Role.xlsx
+++ b/Configs/GameConfig/Datas/Role.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>角色1003</t>
-  </si>
-  <si>
-    <t>Batty_C</t>
   </si>
   <si>
     <t>角色1004</t>
@@ -152,8 +149,8 @@
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -165,6 +162,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -172,7 +199,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,7 +221,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,14 +244,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,6 +266,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -255,16 +282,16 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,37 +299,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,187 +314,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,11 +508,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,22 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,10 +613,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -628,133 +625,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1379,20 +1376,20 @@
       <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="E7" t="s">
-        <v>40</v>
+      <c r="E7">
+        <v>1003</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H7">
-        <v>1002</v>
+        <v>10011</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -1410,7 +1407,7 @@
         <v>1000</v>
       </c>
       <c r="O7">
-        <v>100101</v>
+        <v>100301</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -1418,13 +1415,13 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8">
         <v>13</v>

--- a/Configs/GameConfig/Datas/Role.xlsx
+++ b/Configs/GameConfig/Datas/Role.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>角色1004</t>
-  </si>
-  <si>
-    <t>Batty_D</t>
   </si>
 </sst>
 </file>
@@ -147,10 +144,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -162,17 +159,108 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,15 +272,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,101 +295,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -314,37 +311,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,145 +491,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,30 +502,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -543,6 +516,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -565,8 +558,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,13 +588,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,10 +610,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -625,133 +622,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1420,8 +1417,8 @@
       <c r="D8" t="s">
         <v>37</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
+      <c r="E8">
+        <v>1004</v>
       </c>
       <c r="F8">
         <v>13</v>
@@ -1430,10 +1427,10 @@
         <v>1001</v>
       </c>
       <c r="H8">
-        <v>1002</v>
+        <v>10011</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -1442,7 +1439,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -1451,7 +1448,7 @@
         <v>1000</v>
       </c>
       <c r="O8">
-        <v>100101</v>
+        <v>100401</v>
       </c>
     </row>
   </sheetData>
